--- a/data/trans_orig/IP11C$ingresado-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11C$ingresado-Edad-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -954,102 +954,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1067,102 +1067,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1400,112 +1400,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -1513,112 +1513,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1856,112 +1856,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -1969,112 +1969,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -2312,112 +2312,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -2425,112 +2425,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>51,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3694</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2808</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6385</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>29,04%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>79,2%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9580</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>6746</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11683</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>77,45%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>54,54%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>15008</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>10978</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>17823</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -2768,112 +2768,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>43669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -2881,112 +2881,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3456,112 +3456,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -3569,112 +3569,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3912,112 +3912,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -4025,112 +4025,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,77 +4177,77 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>29,68%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>24,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4217</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5740</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -4368,112 +4368,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -4481,112 +4481,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -4824,112 +4824,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -4937,112 +4937,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5280,112 +5280,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>48560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>76037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -5393,112 +5393,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76231</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -5968,17 +5968,17 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -6043,37 +6043,37 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -6081,112 +6081,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -6424,112 +6424,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -6537,112 +6537,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>737</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>737</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -6880,112 +6880,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -6993,112 +6993,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -7336,112 +7336,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -7449,112 +7449,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -7792,112 +7792,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -7905,112 +7905,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -8480,112 +8480,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -8593,112 +8593,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -8936,52 +8936,52 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9011,37 +9011,37 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -9049,52 +9049,52 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -9124,37 +9124,37 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -9392,112 +9392,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -9505,112 +9505,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -9848,112 +9848,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -9961,112 +9961,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>877</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -10304,112 +10304,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -10417,112 +10417,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
